--- a/data/trans_orig/P57B3_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P57B3_R-Estudios-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>99073</t>
+          <t>111937</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>83996</t>
+          <t>94560</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>114569</t>
+          <t>130086</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>187778</t>
+          <t>208147</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>172909</t>
+          <t>189680</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>207499</t>
+          <t>229199</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>286851</t>
+          <t>320085</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>265083</t>
+          <t>295216</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>312321</t>
+          <t>344189</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>24,64%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>414998</t>
+          <t>465665</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>399502</t>
+          <t>447516</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>430075</t>
+          <t>483042</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>80,73%</t>
+          <t>80,62%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>77,71%</t>
+          <t>77,48%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>83,66%</t>
+          <t>83,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>565172</t>
+          <t>611198</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>545451</t>
+          <t>590146</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>580041</t>
+          <t>629665</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>75,06%</t>
+          <t>74,6%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>72,44%</t>
+          <t>72,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,04%</t>
+          <t>76,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>980170</t>
+          <t>1076862</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>954700</t>
+          <t>1052758</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1001938</t>
+          <t>1101731</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>77,36%</t>
+          <t>77,09%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,35%</t>
+          <t>75,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>79,08%</t>
+          <t>78,87%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>514071</t>
+          <t>577602</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>514071</t>
+          <t>577602</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>514071</t>
+          <t>577602</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>752950</t>
+          <t>819345</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>752950</t>
+          <t>819345</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>752950</t>
+          <t>819345</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1267021</t>
+          <t>1396947</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1267021</t>
+          <t>1396947</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1267021</t>
+          <t>1396947</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>464649</t>
+          <t>250113</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>235573</t>
+          <t>219816</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>916112</t>
+          <t>283607</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>40,02%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>201319</t>
+          <t>239234</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>146179</t>
+          <t>211612</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>235839</t>
+          <t>267980</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>665968</t>
+          <t>489347</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>428213</t>
+          <t>445412</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1416540</t>
+          <t>528074</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>12,01%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1824652</t>
+          <t>1979299</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1373189</t>
+          <t>1945805</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2053728</t>
+          <t>2009596</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>79,7%</t>
+          <t>88,78%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>59,98%</t>
+          <t>87,28%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2034360</t>
+          <t>1929797</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1999840</t>
+          <t>1901051</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2089500</t>
+          <t>1957419</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>88,97%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>87,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>90,24%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>3859012</t>
+          <t>3909096</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3108440</t>
+          <t>3870369</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4096767</t>
+          <t>3953031</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>85,28%</t>
+          <t>88,87%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,7%</t>
+          <t>87,99%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>89,87%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2289301</t>
+          <t>2229412</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2289301</t>
+          <t>2229412</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2289301</t>
+          <t>2229412</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2235679</t>
+          <t>2169031</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2235679</t>
+          <t>2169031</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2235679</t>
+          <t>2169031</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4524980</t>
+          <t>4398443</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4524980</t>
+          <t>4398443</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4524980</t>
+          <t>4398443</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>45612</t>
+          <t>54989</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>34278</t>
+          <t>41708</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>60635</t>
+          <t>69757</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>51393</t>
+          <t>57425</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>41529</t>
+          <t>46403</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>64353</t>
+          <t>71333</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>97005</t>
+          <t>112415</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>81395</t>
+          <t>93869</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>117209</t>
+          <t>133995</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,27%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>601011</t>
+          <t>656598</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>585988</t>
+          <t>641830</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>612345</t>
+          <t>669879</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,62%</t>
+          <t>90,2%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>608331</t>
+          <t>676706</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>595371</t>
+          <t>662798</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>618195</t>
+          <t>687728</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>90,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1209343</t>
+          <t>1333304</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1189139</t>
+          <t>1311724</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1224953</t>
+          <t>1351850</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,03%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,51%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>659724</t>
+          <t>734131</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>659724</t>
+          <t>734131</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>659724</t>
+          <t>734131</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1306348</t>
+          <t>1445719</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1306348</t>
+          <t>1445719</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1306348</t>
+          <t>1445719</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>609334</t>
+          <t>417039</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>380475</t>
+          <t>380052</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1313966</t>
+          <t>459944</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,67 +1789,67 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>440490</t>
+          <t>504807</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>362643</t>
+          <t>470301</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>485113</t>
+          <t>542552</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
+          <t>13,56%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>12,63%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>14,57%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>1243</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>921846</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>874162</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>978274</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>12,73%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
           <t>12,07%</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>9,94%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>13,3%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1243</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1049824</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>809910</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>1902223</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>14,79%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>11,41%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>13,51%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2840662</t>
+          <t>3101562</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2136030</t>
+          <t>3058657</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3069521</t>
+          <t>3138549</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>82,34%</t>
+          <t>88,15%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>61,91%</t>
+          <t>86,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,97%</t>
+          <t>89,2%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,67 +1902,67 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3207862</t>
+          <t>3217701</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3163239</t>
+          <t>3179956</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3285709</t>
+          <t>3252207</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
+          <t>86,44%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>85,43%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>87,37%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>7463</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>6319262</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>6262834</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>6366946</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>87,27%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>86,49%</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
           <t>87,93%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>86,7%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>90,06%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>7463</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>6048524</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>5196125</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>6288438</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>85,21%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>73,2%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>88,59%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3449996</t>
+          <t>3518601</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3449996</t>
+          <t>3518601</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3449996</t>
+          <t>3518601</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3648352</t>
+          <t>3722508</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3648352</t>
+          <t>3722508</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3648352</t>
+          <t>3722508</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7098348</t>
+          <t>7241108</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7098348</t>
+          <t>7241108</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7098348</t>
+          <t>7241108</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
